--- a/inferences/jesuita-entrada-maybe-Coimbra.xlsx
+++ b/inferences/jesuita-entrada-maybe-Coimbra.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>jesuita-entrada.original.comment</t>
+          <t>jesuita-entrada.comment</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -478,12 +478,12 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-lopes-senior</t>
+          <t>deh-inacio-lobo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>António Lopes, sénior</t>
+          <t>Inácio Lobo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -493,12 +493,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Taveiro, diocese de Coimbra</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -513,12 +513,12 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-simoes-i</t>
+          <t>deh-inacio-lobo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>António Simões</t>
+          <t>Inácio Lobo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Rio de Galinhas, diocese de Coimbra</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -548,12 +548,12 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-simoes-iii</t>
+          <t>deh-jose-estevao-de-almeida</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>António Simões</t>
+          <t>José Estêvão de Almeida</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Penela, diocese de Coimbra</t>
+          <t>Esgueira, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17460615</t>
+          <t>16280000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -583,12 +583,12 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>deh-antonio-simoes-iii</t>
+          <t>deh-antonio-lopes-senior</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>António Simões</t>
+          <t>António Lopes, sénior</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -598,12 +598,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Penela, diocese de Coimbra</t>
+          <t>Taveiro, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17460615</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -618,12 +618,12 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>deh-bento-monteiro</t>
+          <t>deh-luis-pinheiro</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bento Monteiro</t>
+          <t>Luís Pinheiro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Esgueira, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17320627</t>
+          <t>16370000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -653,12 +653,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-da-silva-iii</t>
+          <t>deh-luis-pinheiro</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Francisco da Silva</t>
+          <t>Luís Pinheiro</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -668,12 +668,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vinha da Rainha, diocese de Coimbra</t>
+          <t>Esgueira, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17451103</t>
+          <t>16450000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>deh-francisco-moreira</t>
+          <t>deh-joao-couceiro</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Francisco Moreira</t>
+          <t>João Couceiro</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Tentúgal, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17040101</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -723,12 +723,12 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>deh-gregorio-seco</t>
+          <t>deh-jose-soares</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gregório Seco</t>
+          <t>José Soares</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Miranda do Corvo, diocese de Coimbra</t>
+          <t>Santa Comba Dão, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>16730300</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -758,12 +758,12 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>deh-inacio-francisco</t>
+          <t>deh-antonio-simoes-i</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inácio Francisco</t>
+          <t>António Simões</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -773,12 +773,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Conraria, diocese de Coimbra</t>
+          <t>Rio de Galinhas, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17240824</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -793,12 +793,12 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>deh-inacio-lobo</t>
+          <t>deh-francisco-moreira</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Inácio Lobo</t>
+          <t>Francisco Moreira</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>17040101</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -828,12 +828,12 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>deh-inacio-lobo</t>
+          <t>deh-policarpo-de-sousa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Inácio Lobo</t>
+          <t>Policarpo de Sousa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>17121031</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-couceiro</t>
+          <t>deh-inacio-francisco</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>João Couceiro</t>
+          <t>Inácio Francisco</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tentúgal, diocese de Coimbra</t>
+          <t>Conraria, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>17240824</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -898,12 +898,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>deh-joao-da-fonseca-ii</t>
+          <t>deh-bento-monteiro</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>João da Fonseca</t>
+          <t>Bento Monteiro</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Villacova de Suevo, diocese de Coimbra</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17480518</t>
+          <t>17320627</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -968,12 +968,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>deh-joaquim-de-azevedo</t>
+          <t>deh-xavier-duarte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Joaquim de Azevedo</t>
+          <t>Xavier Duarte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17460615</t>
+          <t>17361103</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-da-silva</t>
+          <t>deh-paulo-de-campos</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>José da Silva</t>
+          <t>Paulo de Campos</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Soure, diocese de Coimbra</t>
+          <t>Bobadela, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17400225</t>
+          <t>17370502</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1033,21 +1033,17 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>MMHM:p.375</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-de-almeida-iii</t>
+          <t>deh-gregorio-seco</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>José de Almeida</t>
+          <t>Gregório Seco</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1057,12 +1053,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Arcos, diocese de Coimbra</t>
+          <t>Miranda do Corvo, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1750000</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1077,12 +1073,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-estevao-de-almeida</t>
+          <t>deh-jose-da-silva</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>José Estêvão de Almeida</t>
+          <t>José da Silva</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1092,12 +1088,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Esgueira, diocese de Coimbra</t>
+          <t>Soure, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16280000</t>
+          <t>17400225</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1107,17 +1103,21 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MMHM:p.375</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>deh-jose-soares</t>
+          <t>deh-mateus-de-figueiredo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>José Soares</t>
+          <t>Mateus de Figueiredo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1127,12 +1127,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Santa Comba Dão, diocese de Coimbra</t>
+          <t>S. Joaninho, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16730300</t>
+          <t>17440404</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1147,12 +1147,12 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>deh-luis-de-carvalho-ii</t>
+          <t>deh-francisco-da-silva-iii</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Luís de Carvalho</t>
+          <t>Francisco da Silva</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Miranda do Corvo, diocese de Coimbra</t>
+          <t>Vinha da Rainha, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17490327</t>
+          <t>17451103</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1217,12 +1217,12 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>deh-luis-pinheiro</t>
+          <t>deh-joaquim-de-azevedo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Luís Pinheiro</t>
+          <t>Joaquim de Azevedo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Esgueira, diocese de Coimbra</t>
+          <t>Coimbra</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16370000</t>
+          <t>17460615</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>deh-luis-pinheiro</t>
+          <t>deh-antonio-simoes-iii</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Luís Pinheiro</t>
+          <t>António Simões</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Esgueira, diocese de Coimbra</t>
+          <t>Penela, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16450000</t>
+          <t>17460615</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1287,12 +1287,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-da-costa</t>
+          <t>deh-antonio-simoes-iii</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Manuel da Costa</t>
+          <t>António Simões</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Figueiró, diocese de Coimbra</t>
+          <t>Penela, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17481209</t>
+          <t>17460615</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>deh-manuel-de-carvalho-ii</t>
+          <t>deh-tome-da-silva</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Manuel de Carvalho</t>
+          <t>Tomé da Silva</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Águeda, diocese de Coimbra</t>
+          <t>Sousa, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17470102</t>
+          <t>17460719</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1352,21 +1352,17 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>talvez tenha saído durante o noviciado</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>deh-mateus-de-figueiredo</t>
+          <t>deh-manuel-de-carvalho-ii</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mateus de Figueiredo</t>
+          <t>Manuel de Carvalho</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1376,12 +1372,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>S. Joaninho, diocese de Coimbra</t>
+          <t>Águeda, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17440404</t>
+          <t>17470102</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1390,18 +1386,26 @@
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>para a China</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>talvez tenha saído durante o noviciado</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>deh-paulo-de-campos</t>
+          <t>deh-joao-da-fonseca-ii</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Paulo de Campos</t>
+          <t>João da Fonseca</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1411,12 +1415,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bobadela, diocese de Coimbra</t>
+          <t>Villacova de Suevo, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17370502</t>
+          <t>17480518</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1431,12 +1435,12 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>deh-policarpo-de-sousa</t>
+          <t>deh-manuel-da-costa</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Policarpo de Sousa</t>
+          <t>Manuel da Costa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1446,12 +1450,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Figueiró, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17121031</t>
+          <t>17481209</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1466,12 +1470,12 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>deh-tome-da-silva</t>
+          <t>deh-luis-de-carvalho-ii</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tomé da Silva</t>
+          <t>Luís de Carvalho</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1481,12 +1485,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sousa, diocese de Coimbra</t>
+          <t>Miranda do Corvo, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17460719</t>
+          <t>17490327</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1501,12 +1505,12 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>deh-xavier-duarte</t>
+          <t>deh-jose-de-almeida-iii</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Xavier Duarte</t>
+          <t>José de Almeida</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1516,12 +1520,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Coimbra</t>
+          <t>Arcos, diocese de Coimbra</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17361103</t>
+          <t>1750000</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
